--- a/planilha_padrao.xlsx
+++ b/planilha_padrao.xlsx
@@ -699,7 +699,7 @@
         <v>20</v>
       </c>
       <c r="F3" s="7">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="G3" s="7">
         <v>20</v>
@@ -711,7 +711,7 @@
         <v>100</v>
       </c>
       <c r="J3" s="6">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="K3" s="7">
         <v>4</v>
@@ -806,7 +806,7 @@
         <v>100</v>
       </c>
       <c r="J4" s="6">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="K4" s="7">
         <v>4</v>
@@ -901,7 +901,7 @@
         <v>100</v>
       </c>
       <c r="J5" s="6">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="K5" s="7">
         <v>4</v>
@@ -996,7 +996,7 @@
         <v>100</v>
       </c>
       <c r="J6" s="6">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="K6" s="7">
         <v>4</v>
@@ -1091,7 +1091,7 @@
         <v>100</v>
       </c>
       <c r="J7" s="6">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="K7" s="7">
         <v>4</v>
@@ -1186,7 +1186,7 @@
         <v>100</v>
       </c>
       <c r="J8" s="6">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="K8" s="7">
         <v>4</v>
@@ -1281,7 +1281,7 @@
         <v>100</v>
       </c>
       <c r="J9" s="6">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="K9" s="7">
         <v>4</v>
@@ -1376,7 +1376,7 @@
         <v>100</v>
       </c>
       <c r="J10" s="6">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="K10" s="7">
         <v>4</v>
@@ -1471,7 +1471,7 @@
         <v>100</v>
       </c>
       <c r="J11" s="6">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="K11" s="7">
         <v>4</v>
@@ -1566,7 +1566,7 @@
         <v>100</v>
       </c>
       <c r="J12" s="6">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="K12" s="7">
         <v>4</v>
